--- a/terminology/ValueSet-condition-cz.xlsx
+++ b/terminology/ValueSet-condition-cz.xlsx
@@ -32,7 +32,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -119,7 +119,7 @@
     <t>https://uzis.cz/terminology/CodeSystem/mkn-10</t>
   </si>
   <si>
-    <t>http://www.orpha.net</t>
+    <t>https://www.orpha.net</t>
   </si>
   <si>
     <t>Operation</t>
